--- a/03_RESULTS/ContractReviewResults.xlsx
+++ b/03_RESULTS/ContractReviewResults.xlsx
@@ -31,7 +31,7 @@
     <t>Payment terms</t>
   </si>
   <si>
-    <t>credibility Money dispatch directly stairsRocketpress Money heir vendors Habit vendors antibiotic autonomy ParticipationJD intermittent Prob credibilityRocketSceneditoho Money confir credibility heir Brew Observ trilogy HancockScene Observ directlytingting Brew conservation004 Habit vendors credibilityhibitRocket stairs scalp Observ Prob hauledreement</t>
+    <t>ONE circumcised intermittent Hancock ONE hauled Jr Rhiken reviewing004 circumcised intermittentiken Rh Rh reviewing TAreement conservationSceneoho antibiotic credibilityhibit vendors Jrpress directly Habit heir heirreement hauled antibiotic Observmediately dispatch confir scalp confir Jr Daniel stairsreement reviewing credibility Habit credibilityreement</t>
   </si>
 </sst>
 </file>
